--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484887_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484887_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6015</v>
+        <v>8.2037</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8427</v>
+        <v>5.6036</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7588</v>
+        <v>2.6001</v>
       </c>
       <c r="G2" t="n">
         <v>6.3102</v>
@@ -610,13 +610,13 @@
         <v>3.774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8976</v>
+        <v>-0.2954</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9254</v>
+        <v>-0.1644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0277</v>
+        <v>-0.131</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6415999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8705</v>
+        <v>1.8158</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0373</v>
+        <v>0.8239</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.9919</v>
       </c>
       <c r="G3" t="n">
         <v>2.147</v>
@@ -688,13 +688,13 @@
         <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1634</v>
+        <v>-0.2181</v>
       </c>
       <c r="T3" t="n">
-        <v>0.479</v>
+        <v>0.2656</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6424</v>
+        <v>-0.4837</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3018</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1999</v>
+        <v>1.5409</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7005</v>
+        <v>1.9356</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5006</v>
+        <v>-0.3948</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0295</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6008</v>
+        <v>-0.2598</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1147</v>
+        <v>0.1205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4861</v>
+        <v>-0.3803</v>
       </c>
       <c r="V4" t="n">
         <v>2.2076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUÑOZ</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9509</v>
+        <v>0.9616</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9509</v>
+        <v>-0.1559</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.1174</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9509</v>
+        <v>0.5022</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9509</v>
+        <v>-0.673</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.1752</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9509</v>
+        <v>0.6067</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9509</v>
+        <v>-0.2004</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.1045</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.4727</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.3682</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.4841</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.1208</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3632</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>J. MARTINEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8328</v>
+        <v>0.9509</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1884</v>
+        <v>0.9509</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0212</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3073</v>
+        <v>0.9509</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.3855</v>
+        <v>0.9509</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0782</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3556</v>
+        <v>0.9509</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.376</v>
+        <v>0.9509</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7316</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6629</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0095</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3466</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1357</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4763</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2065</v>
+        <v>0.3323</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.858</v>
+        <v>-0.2657</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0645</v>
+        <v>0.598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5022</v>
+        <v>-0.3073</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.673</v>
+        <v>-3.3855</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1752</v>
+        <v>3.0782</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6067</v>
+        <v>0.3556</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2004</v>
+        <v>-2.376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.7316</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1045</v>
+        <v>-0.6629</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4727</v>
+        <v>-1.0095</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3682</v>
+        <v>0.3466</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2392</v>
+        <v>0.1114</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.823</v>
+        <v>0.0584</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4161</v>
+        <v>0.053</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>1.2072</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5074</v>
+        <v>-0.4486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2305</v>
+        <v>-0.1718</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2768</v>
@@ -1078,10 +1078,10 @@
         <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1887</v>
+        <v>0.2475</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1052</v>
+        <v>-0.0465</v>
       </c>
       <c r="U8" t="n">
         <v>0.2939</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3657</v>
+        <v>-2.3606</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9196</v>
+        <v>-1.8352</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.446</v>
+        <v>-0.5254</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2709</v>
@@ -1156,13 +1156,13 @@
         <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9617</v>
+        <v>-0.0332</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2432</v>
+        <v>0.3277</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2815</v>
+        <v>-0.3609</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8678</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7417</v>
+        <v>-2.4091</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6601</v>
+        <v>-0.3276</v>
       </c>
       <c r="F10" t="n">
         <v>-2.0816</v>
@@ -1234,10 +1234,10 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.696</v>
+        <v>-0.3634</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6343</v>
+        <v>-0.3017</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0617</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1753</v>
+        <v>-2.7588</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0926</v>
+        <v>0.1917</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.268</v>
+        <v>-2.9505</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7522</v>
@@ -1312,13 +1312,13 @@
         <v>2.0757</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3857</v>
+        <v>0.0308</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3121</v>
+        <v>0.4111</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6978</v>
+        <v>-0.3803</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9244</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0955</v>
+        <v>-6.288</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1784</v>
+        <v>-3.3973</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9171</v>
+        <v>-2.8906</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9885</v>
@@ -1390,13 +1390,13 @@
         <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8424</v>
+        <v>-0.0348</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4674</v>
+        <v>0.3137</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.375</v>
+        <v>-0.3485</v>
       </c>
       <c r="V12" t="n">
         <v>2.5094</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2235</v>
+        <v>-0.459900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>1.589</v>
+        <v>3.3522</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8124</v>
+        <v>-3.8123</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0669</v>
@@ -1438,7 +1438,7 @@
         <v>-10.158</v>
       </c>
       <c r="I13" t="n">
-        <v>9.091100000000001</v>
+        <v>9.091099999999997</v>
       </c>
       <c r="J13" t="n">
         <v>13.058</v>
@@ -1465,13 +1465,13 @@
         <v>-17.9265</v>
       </c>
       <c r="R13" t="n">
-        <v>20.757</v>
+        <v>20.75700000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0627</v>
+        <v>-1.2991</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8999999999999999</v>
+        <v>0.8636</v>
       </c>
       <c r="U13" t="n">
         <v>-2.1627</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6227</v>
+        <v>6.5396</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8926</v>
+        <v>4.6003</v>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.9393</v>
       </c>
       <c r="G14" t="n">
         <v>2.5996</v>
@@ -1546,13 +1546,13 @@
         <v>3.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4303</v>
+        <v>0.3473</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2068</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2235</v>
+        <v>0.4328</v>
       </c>
       <c r="V14" t="n">
         <v>1.1397</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.884</v>
+        <v>1.6265</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4355</v>
+        <v>0.1445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4485</v>
+        <v>1.482</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9992</v>
+        <v>-0.1915</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2978</v>
+        <v>1.523</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2986</v>
+        <v>-1.7144</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0093</v>
+        <v>1.0386</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8362</v>
+        <v>1.6059</v>
       </c>
       <c r="L15" t="n">
-        <v>0.173</v>
+        <v>-0.5673</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.01</v>
+        <v>-1.23</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5384</v>
+        <v>-0.0829</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4716</v>
+        <v>-1.1471</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.8497</v>
+        <v>1.5096</v>
       </c>
       <c r="Q15" t="n">
-        <v>-8.4915</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5008</v>
+        <v>0.1121</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5596</v>
+        <v>-0.2524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9413</v>
+        <v>0.3645</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2337</v>
+        <v>0.1963</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3582</v>
+        <v>0.3018</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1245</v>
+        <v>-0.1055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>L. CARRIÓN GALINDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4256</v>
+        <v>1.2509</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0471</v>
+        <v>1.2509</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3786</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1915</v>
+        <v>1.2509</v>
       </c>
       <c r="H16" t="n">
-        <v>1.523</v>
+        <v>0.6339</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7144</v>
+        <v>0.617</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0386</v>
+        <v>1.2509</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6059</v>
+        <v>0.6339</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5673</v>
+        <v>0.617</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.23</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0829</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1471</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0888</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3498</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1963</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. CARRIÓN GALINDO</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2509</v>
+        <v>1.2395</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2509</v>
+        <v>0.2407</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.9988</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2509</v>
+        <v>1.9992</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6339</v>
+        <v>3.2978</v>
       </c>
       <c r="I17" t="n">
-        <v>0.617</v>
+        <v>-1.2986</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2509</v>
+        <v>4.0093</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6339</v>
+        <v>3.8362</v>
       </c>
       <c r="L17" t="n">
-        <v>0.617</v>
+        <v>0.173</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.5384</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.4716</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-5.8497</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-8.4915</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.8562</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.3647</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.4915</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.2337</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.3582</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DIAZ GALIAN</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9658</v>
+        <v>1.2003</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3237</v>
+        <v>0.2503</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3578</v>
+        <v>0.95</v>
       </c>
       <c r="G18" t="n">
-        <v>0.151</v>
+        <v>-0.0398</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7615</v>
+        <v>1.9299</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.9697</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7865</v>
+        <v>1.9276</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1199</v>
+        <v>2.4041</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6666</v>
+        <v>-0.4765</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6354</v>
+        <v>-1.9674</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3584</v>
+        <v>-0.4742</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.277</v>
+        <v>-1.4932</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1887</v>
+        <v>3.5853</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8523</v>
+        <v>0.3079</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5372</v>
+        <v>-0.0731</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3151</v>
+        <v>0.381</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2262</v>
+        <v>-0.7661</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2262</v>
+        <v>-1.0489</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>R. DIAZ GALIAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.1251</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2369</v>
+        <v>2.6416</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9258999999999999</v>
+        <v>-2.5166</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0398</v>
+        <v>0.151</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9299</v>
+        <v>0.7615</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9697</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9276</v>
+        <v>1.7865</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4041</v>
+        <v>1.1199</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4765</v>
+        <v>0.6666</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9674</v>
+        <v>-1.6354</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4742</v>
+        <v>-0.3584</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4932</v>
+        <v>-1.277</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5853</v>
+        <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2034</v>
+        <v>1.0115</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5603</v>
+        <v>0.8551</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3569</v>
+        <v>0.1564</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7661</v>
+        <v>-1.2262</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0489</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4051</v>
+        <v>-0.1266</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1439</v>
+        <v>0.5593</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7388</v>
+        <v>-0.6859</v>
       </c>
       <c r="G20" t="n">
         <v>-0.623</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0281</v>
+        <v>0.4964</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1228</v>
+        <v>0.5382</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5942</v>
+        <v>-0.905</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3747</v>
+        <v>-0.0824</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2195</v>
+        <v>-0.8227</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9227</v>
@@ -2092,13 +2092,13 @@
         <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3698</v>
+        <v>0.3193</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.09</v>
+        <v>0.2023</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2798</v>
+        <v>0.117</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4027</v>
+        <v>-3.1308</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3336</v>
+        <v>-2.1387</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0691</v>
+        <v>-0.9921</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5521</v>
@@ -2170,13 +2170,13 @@
         <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1875</v>
+        <v>0.4594</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5596</v>
+        <v>0.7544</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.372</v>
+        <v>-0.295</v>
       </c>
       <c r="V22" t="n">
         <v>0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0227</v>
+        <v>-4.9462</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3363</v>
+        <v>-3.6543</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6864</v>
+        <v>-1.292</v>
       </c>
       <c r="G23" t="n">
         <v>0.3952</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2744</v>
+        <v>-0.198</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.823</v>
+        <v>-0.141</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4514</v>
+        <v>-0.057</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2565</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.2235</v>
+        <v>2.8733</v>
       </c>
       <c r="E24" t="n">
-        <v>3.812199999999999</v>
+        <v>3.8122</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5886</v>
+        <v>-0.9392</v>
       </c>
       <c r="G24" t="n">
-        <v>1.066800000000001</v>
+        <v>1.0668</v>
       </c>
       <c r="H24" t="n">
         <v>10.1581</v>
@@ -2326,16 +2326,16 @@
         <v>17.9265</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0626</v>
+        <v>3.7121</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1629</v>
+        <v>2.1627</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9000999999999997</v>
+        <v>1.5495</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9245000000000001</v>
+        <v>0.9244999999999992</v>
       </c>
       <c r="W24" t="n">
         <v>8.281600000000001</v>
